--- a/www/terminologies/ASS-A30-TypeAutorisation-Profession-EPARS.xlsx
+++ b/www/terminologies/ASS-A30-TypeAutorisation-Profession-EPARS.xlsx
@@ -110,13 +110,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R17-TypeAutorisation/FHIR/TRE-R17-TypeAutorisation|20250523120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R17-TypeAutorisation/FHIR/TRE-R17-TypeAutorisation</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_G15-ProfessionSante/FHIR/TRE-G15-ProfessionSante|20250328120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G15-ProfessionSante/FHIR/TRE-G15-ProfessionSante</t>
   </si>
   <si>
     <t>AM01</t>
@@ -215,13 +215,13 @@
     <t>AM41</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial|20241213120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R94-ProfessionSocial/FHIR/TRE-R94-ProfessionSocial</t>
   </si>
   <si>
     <t>41</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre|20241213120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R95-UsagerTitre/FHIR/TRE-R95-UsagerTitre</t>
   </si>
   <si>
     <t>71</t>
